--- a/data/Smoking_Dataset_Cleaned.xlsx
+++ b/data/Smoking_Dataset_Cleaned.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF5"/>
+  <dimension ref="A1:BV5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>url or link to pdf</t>
+          <t>StudyID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -429,338 +429,412 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Study Design Type</t>
+          <t>Pos Result Y/N</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Pos Result Y/N</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>metric</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>metric</t>
+          <t>measure</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>measure</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PVal</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>PVal</t>
+          <t>Clincial Trial YN</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Clincial Trial YN</t>
+          <t>RandomizationYN</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>RandomizationYN</t>
+          <t>BlindingYN</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>BlindingYN</t>
+          <t>Double+Blind</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Double+Blind</t>
+          <t>Comparator</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Comparator</t>
+          <t>SampleSize_NFinal</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>SampleSize_NFinal</t>
+          <t>PrimaryCare</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>PrimaryCare</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Retention (%)</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Retention (%)</t>
+          <t>ConfoundYN</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>ConfoundYN</t>
+          <t>InclusionExclusionCriteria</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>InclusionExclusionCriteria</t>
+          <t>ValidatedScaleMeasYN</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>ValidatedScaleMeasYN</t>
+          <t>MethodologyDescribedYN</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>MethodologyDescribedYN</t>
+          <t>Funding/COI YN</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Funding/COI YN</t>
+          <t>BaseStatus</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>BaseStatus</t>
+          <t>Age_Median</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Age_Median</t>
+          <t>PercentFem</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>PercentFem</t>
+          <t>RaceEthnicity_BIPOCPercent</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>RaceEthnicity_BIPOCPercent</t>
+          <t>SocioeconomicStatusYN</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>SocioeconomicStatusYN</t>
+          <t>Country_USvsNonUS</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>Country_USvsNonUS</t>
+          <t>RecruitmentRepresentYN</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>RecruitmentRepresentYN</t>
+          <t>InterventionDescription</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>InterventionDescription</t>
+          <t>InterventionTherapy</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>InterventionTherapy</t>
+          <t>HarmsAssessed</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>HarmsAssessed</t>
+          <t>CulturalFraming</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>CulturalFraming</t>
+          <t>IndigenousFramework</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>IndigenousFramework</t>
+          <t>Reciprocity</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>Reciprocity</t>
+          <t>Followup in months</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>Followup in months</t>
+          <t>BehaviorChangeMeasured</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>BehaviorChangeMeasured</t>
+          <t>PhysicalChangeMeasured</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>PhysicalChangeMeasured</t>
+          <t>MentalHealthChangeMeasured</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>MentalHealthChangeMeasured</t>
+          <t>QualityOfLifeMeasured</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>QualityOfLifeMeasured</t>
+          <t>Implementation Outcome</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>Implementation Outcome</t>
+          <t>ReductionMeasured</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>ReductionMeasured</t>
+          <t>CessationMeasured</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>CessationMeasured</t>
+          <t>RelapseMeasured</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>RelapseMeasured</t>
+          <t>MortalityMeasured</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>MortalityMeasured</t>
+          <t>Psilocybin</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>Psilocybin</t>
+          <t>Ayahuasca</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>Ayahuasca</t>
+          <t>LSD</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>LSD</t>
+          <t>Mescaline</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>Mescaline</t>
+          <t>Ibogaine</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>Ibogaine</t>
+          <t>MDMA</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>MDMA</t>
+          <t>Ketamine</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>Ketamine</t>
+          <t>Cannabis</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>Cannabis</t>
+          <t>OtherPsychedelic</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>OtherPsychedelic</t>
+          <t>MultiplePsychedelic</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>MultiplePsychedelic</t>
+          <t>EligibleYN</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>EligibilityFailedCriterion</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>EligibilityNote</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>SafetyReported</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>AnyAEReported</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>NumDistinctAEs</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>NParticipantsWithAE</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>AE_denominator</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>ArmScope</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>WorstSeverity</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>text_source</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>text_format</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>PromptVersion</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>RubricVersion</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>Temperature</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>SourcePDF</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://jamanetwork.com/journals/jamanetworkopen/fullarticle/2846155</t>
+          <t>Garcia-Romeu 2015</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Johnson MW, Naudé GP, Hendricks PS, Garcia-Romeu A. Psilocybin or Nicotine Patch for Smoking Cessation: A Pilot Randomized Clinical Trial. JAMA Netw Open. 2026;9(3):e260972. doi:10.1001/jamanetworkopen.2026.0972</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>Garcia-Romeu, A., Griffiths, R. R., &amp; Johnson, M. W. (2015). Psilocybin-occasioned mystical experiences in the treatment of tobacco addiction. Current Drug Abuse Reviews, 7(3), 157-164.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>Smoking</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Clinical Trial</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
+      <c r="D2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>12/15 (80%) biologically verified 7-day point-prevalence smoking abstinence at 6-month follow-up (single-arm, descriptive rate carried over from the parent trial)</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>OR 6.12</t>
+          <t>Abstinence rate (%)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Odds ratio</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1.99-23.26</t>
-        </is>
-      </c>
+          <t>12/15 (80%)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>0.003</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -768,20 +842,22 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
-        <v>1</v>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="Q2" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
@@ -790,32 +866,42 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>33.3</v>
+      </c>
       <c r="AB2" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="AC2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="AF2" t="n">
-        <v>0</v>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Oral psilocybin, moderate (20mg/70kg, week 5) and high (30mg/70kg, week 7, optional week 13) doses, within 15-week CBT-based smoking-cessation therapy incorporating mindfulness and guided imagery.</t>
+        </is>
       </c>
       <c r="AG2" t="n">
         <v>1</v>
@@ -824,7 +910,7 @@
         <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
@@ -832,11 +918,13 @@
       <c r="AK2" t="n">
         <v>0</v>
       </c>
-      <c r="AL2" t="n">
-        <v>0</v>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="AM2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AN2" t="n">
         <v>1</v>
@@ -845,28 +933,28 @@
         <v>1</v>
       </c>
       <c r="AP2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
         <v>1</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -892,60 +980,126 @@
       <c r="BE2" t="n">
         <v>0</v>
       </c>
-      <c r="BF2" t="n">
-        <v>0</v>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>psychedelic_arm</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>born-digital</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>markdown</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>v1.2</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="BU2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>smoking/nihms-648744.pdf</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4342293/</t>
+          <t>Johnson 2014</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Garcia‑Romeu, A., Griffiths, R. R., &amp; Johnson, M. W. (2015). Psilocybin‑occasioned mystical experiences in the treatment of tobacco addiction. *Current Drug Abuse Reviews*, 7(3), 157–164. https://doi.org/10.2174/1874473708666150107121331</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2015</v>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>Johnson, M. W., Garcia-Romeu, A., Cosimano, M. P., &amp; Griffiths, R. R. (2014). Pilot study of the 5-HT2AR agonist psilocybin in the treatment of tobacco addiction. Journal of Psychopharmacology, 28(11), 983-992.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Smoking</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Clinical Trial</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
+      <c r="D3" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>12/15 (80%) biologically verified 7-day point-prevalence smoking abstinence at 6-month follow-up</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SOCQ: quitters 65.8 (2.8) vs 52.1 (7.9)</t>
+          <t>Abstinence rate (%)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Group means (quitters vs non-quitters)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>65.8 vs 52.1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>t, df: 2.02, 40</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>12/15 (80%)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -956,56 +1110,66 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Does not apply</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>33.3</v>
+      </c>
       <c r="AB3" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="AC3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="AF3" t="n">
-        <v>0</v>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Oral psilocybin, moderate (20mg/70kg, week 5) and high (30mg/70kg, weeks 7 and optionally 13) doses, within 15-week CBT-based smoking-cessation protocol with preparation, integration, and support meetings.</t>
+        </is>
       </c>
       <c r="AG3" t="n">
         <v>1</v>
@@ -1014,7 +1178,7 @@
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
@@ -1022,17 +1186,19 @@
       <c r="AK3" t="n">
         <v>0</v>
       </c>
-      <c r="AL3" t="n">
-        <v>0</v>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="AM3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AN3" t="n">
         <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
@@ -1041,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS3" t="n">
         <v>1</v>
@@ -1053,10 +1219,10 @@
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
@@ -1082,54 +1248,122 @@
       <c r="BE3" t="n">
         <v>0</v>
       </c>
-      <c r="BF3" t="n">
-        <v>0</v>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>psychedelic_arm</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>Mild</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>born-digital</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>markdown</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>v1.2</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="BU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>smoking/nihms648730.pdf</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.tandfonline.com/doi/abs/10.3109/00952990.2016.1170135</t>
+          <t>Johnson 2016</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Johnson, M. W., Garcia-Romeu, A., &amp; Griffiths, R. R. (2017). Long-term follow-up of psilocybin-facilitated smoking cessation. The American Journal of Drug and Alcohol Abuse, 43(1), 55–60. https://doi.org/10.3109/00952990.2016.1170135</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+          <t>Johnson, M. W., Garcia-Romeu, A., &amp; Griffiths, R. R. (2016). Long-term follow-up of psilocybin-facilitated smoking cessation. American Journal of Drug and Alcohol Abuse, 43(1), 55-60.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Smoking</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>2016</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Smoking</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Clinical Trial</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>9/15 (60%) biologically verified (breath CO + urine cotinine + TLFB) smoking abstinence at long-term follow-up (mean 30 months post-TQD, range 16-57 months; single-arm, no comparator)</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>60% abstinent @ 30 mo</t>
+          <t>Abstinence rate (%)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Abstinence rate (%)</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>60</v>
-      </c>
+          <t>9/15 (60%)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -1140,54 +1374,64 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
       </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="n">
-        <v>33</v>
-      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="AF4" t="n">
-        <v>0</v>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Oral psilocybin (20mg/70kg wk5, 30mg/70kg wk7, optional 30mg/70kg wk13) within 15-week CBT-based smoking-cessation program with mindfulness and guided imagery.</t>
+        </is>
       </c>
       <c r="AG4" t="n">
         <v>1</v>
@@ -1196,7 +1440,7 @@
         <v>1</v>
       </c>
       <c r="AI4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
@@ -1204,11 +1448,13 @@
       <c r="AK4" t="n">
         <v>0</v>
       </c>
-      <c r="AL4" t="n">
-        <v>0</v>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="AM4" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="AN4" t="n">
         <v>1</v>
@@ -1222,9 +1468,11 @@
       <c r="AQ4" t="n">
         <v>0</v>
       </c>
-      <c r="AR4" t="inlineStr"/>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT4" t="n">
         <v>1</v>
@@ -1233,10 +1481,10 @@
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
@@ -1262,52 +1510,130 @@
       <c r="BE4" t="n">
         <v>0</v>
       </c>
-      <c r="BF4" t="n">
-        <v>0</v>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>psychedelic_arm</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>born-digital</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>markdown</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>v1.2</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="BU4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>smoking/johnson2016.pdf</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC4286320/</t>
+          <t>Johnson MW 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Johnson, M. W., Garcia-Romeu, A., Cosimano, M. P., &amp; Griffiths, R. R. (2014). Pilot study of the 5-HT2AR agonist psilocybin in the treatment of tobacco addiction. Journal of psychopharmacology (Oxford, England), 28(11), 983–992. https://doi.org/10.1177/0269881114548296</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2014</v>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>Johnson MW, Naude, G. P., Hendricks, P. S., &amp; Garcia-Romeu, A. (2026). Psilocybin or nicotine patch for smoking cessation: A pilot randomized clinical trial. JAMA Network Open.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Smoking</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Clinical Trial</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
+      <c r="D5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>OR = 6.12</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>80% abstience @ 6mo</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Abstinence rate (%)</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>80</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>Odds ratio</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>95% CI, 1.99-23.26</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
       <c r="L5" t="n">
         <v>1</v>
       </c>
@@ -1318,25 +1644,27 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>1</v>
@@ -1347,23 +1675,37 @@
       <c r="X5" t="n">
         <v>1</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>30-50</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>40.2</v>
+      </c>
       <c r="AB5" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Single 30 mg/70 kg oral psilocybin dose during a supervised ~8-9 hour session (eyeshades, music) plus 13-week manualized CBT; comparator arm received 8-10 weeks nicotine patch plus CBT.</t>
+        </is>
       </c>
       <c r="AG5" t="n">
         <v>1</v>
@@ -1372,7 +1714,7 @@
         <v>1</v>
       </c>
       <c r="AI5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
@@ -1380,17 +1722,19 @@
       <c r="AK5" t="n">
         <v>0</v>
       </c>
-      <c r="AL5" t="n">
-        <v>0</v>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="AM5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AN5" t="n">
         <v>1</v>
       </c>
       <c r="AO5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -1398,7 +1742,9 @@
       <c r="AQ5" t="n">
         <v>0</v>
       </c>
-      <c r="AR5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
       <c r="AS5" t="n">
         <v>1</v>
       </c>
@@ -1406,13 +1752,13 @@
         <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
@@ -1438,8 +1784,80 @@
       <c r="BE5" t="n">
         <v>0</v>
       </c>
-      <c r="BF5" t="n">
-        <v>0</v>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>Not numbered</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>pooled</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>born-digital</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>markdown</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>claude-sonnet-5</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>v1.2</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="BU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>smoking/johnson_2026_oi_260062_1772564464.70221 (1).pdf</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/Smoking_Dataset_Cleaned.xlsx
+++ b/data/Smoking_Dataset_Cleaned.xlsx
@@ -812,7 +812,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12/15 (80%) biologically verified 7-day point-prevalence smoking abstinence at 6-month follow-up (single-arm, descriptive rate carried over from the parent trial)</t>
+          <t>SOCQ: quitters 65.8 (2.8) vs 52.1 (7.9)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -825,7 +825,11 @@
           <t>12/15 (80%)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>t, df: 2.02, 40</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>1</v>
@@ -866,7 +870,7 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
@@ -930,7 +934,7 @@
         <v>1</v>
       </c>
       <c r="AO2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
@@ -1134,7 +1138,7 @@
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
         <v>1</v>
@@ -1398,7 +1402,7 @@
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
@@ -1655,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>82.90000000000001</v>
@@ -1692,7 +1696,7 @@
         <v>11</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>

--- a/data/Smoking_Dataset_Cleaned.xlsx
+++ b/data/Smoking_Dataset_Cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV5"/>
+  <dimension ref="A1:BW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -719,70 +719,75 @@
       </c>
       <c r="BI1" t="inlineStr">
         <is>
+          <t>BaseStatusReportedYN</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
           <t>SafetyReported</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>AnyAEReported</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>NumDistinctAEs</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>NParticipantsWithAE</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>AE_denominator</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>ArmScope</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>WorstSeverity</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>text_source</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>text_format</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>PromptVersion</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>RubricVersion</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>Temperature</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>SourcePDF</t>
         </is>
@@ -993,68 +998,73 @@
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>Mild</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BV2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW2" t="inlineStr">
         <is>
           <t>smoking/nihms-648744.pdf</t>
         </is>
@@ -1261,64 +1271,69 @@
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr">
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>Mild</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BV3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW3" t="inlineStr">
         <is>
           <t>smoking/nihms648730.pdf</t>
         </is>
@@ -1523,68 +1538,73 @@
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>psychedelic_arm</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BV4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW4" t="inlineStr">
         <is>
           <t>smoking/johnson2016.pdf</t>
         </is>
@@ -1797,68 +1817,73 @@
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>Not numbered</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>pooled</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>born-digital</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>claude-sonnet-5</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>v1.2</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>v1</t>
         </is>
       </c>
-      <c r="BU5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BV5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW5" t="inlineStr">
         <is>
           <t>smoking/johnson_2026_oi_260062_1772564464.70221 (1).pdf</t>
         </is>
